--- a/artfynd/A 23767-2026 artfynd.xlsx
+++ b/artfynd/A 23767-2026 artfynd.xlsx
@@ -675,67 +675,55 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>175596</v>
+        <v>110268662</v>
       </c>
       <c r="B2" t="n">
-        <v>78528</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>81531</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>515</v>
+        <v>145</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blylav</t>
+          <t>Klosterlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pectenia plumbea</t>
+          <t>Biatoridium monasteriense</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Lightf.) P.M.Jørg. et al.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>J.Lahm ex Körb.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
           <t>med apothecier</t>
         </is>
       </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lådnaön, Upl</t>
+          <t>Lådnaön, lövskog NV Sviudden, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>711125.7006365537</v>
+        <v>711110</v>
       </c>
       <c r="R2" t="n">
-        <v>6592433.015528592</v>
+        <v>6592415</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,27 +747,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2008-07-08</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-21</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2008-07-08</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>I ögonhöjd på gammal ask ca 380m väst Skomakarviken.NÖ delen av nyckelbiotopen 10J 8d 12 i Skogsstyrelsens register.</t>
+          <t>2023-06-21</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,79 +761,94 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Lövskogslund</t>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Lövskog</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Rikard Anderberg</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Rikard Anderberg, Fingal Gyllang</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>66786499</v>
+        <v>110269389</v>
       </c>
       <c r="B3" t="n">
-        <v>97512</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>81531</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>174</v>
+        <v>145</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Strävlosta</t>
+          <t>Klosterlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bromopsis benekenii</t>
+          <t>Biatoridium monasteriense</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Lange) Holub</t>
+          <t>J.Lahm ex Körb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lådnaön, Upl</t>
+          <t>Lövlund, LÅdnaön, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>711397.047932506</v>
+        <v>711105</v>
       </c>
       <c r="R3" t="n">
-        <v>6592122.29277597</v>
+        <v>6592425</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -884,22 +872,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2017-07-20</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2017-07-20</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-21</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -914,27 +892,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Patrik Engström</t>
+          <t>Fingal Gyllang</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Patrik Engström</t>
+          <t>Fingal Gyllang, Rikard Anderberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>66786502</v>
+        <v>66786499</v>
       </c>
       <c r="B4" t="n">
-        <v>98431</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100347</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -942,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222771</v>
+        <v>174</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Strävlosta</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Bromopsis benekenii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Lange) Holub</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -969,10 +942,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>711397.047932506</v>
+        <v>711397</v>
       </c>
       <c r="R4" t="n">
-        <v>6592122.29277597</v>
+        <v>6592122</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1002,19 +975,9 @@
           <t>2017-07-20</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2017-07-20</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1041,55 +1004,60 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>67171938</v>
+        <v>86340912</v>
       </c>
       <c r="B5" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100347</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>174</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Strävlosta</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bromopsis benekenii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(Lange) Holub</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lövskogslund, Lådnaön, Gällnö skärgård, Upl</t>
+          <t>Lådnaön, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>711270.0789314739</v>
+        <v>711300</v>
       </c>
       <c r="R5" t="n">
-        <v>6592254.425700218</v>
+        <v>6592236</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1113,22 +1081,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2017-08-12</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-06-18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2017-08-12</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-06-18</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1137,72 +1095,78 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Fingal Gyllang</t>
+          <t>Patrik Engström</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Fingal Gyllang</t>
+          <t>Patrik Engström</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>72467065</v>
+        <v>175596</v>
       </c>
       <c r="B6" t="n">
-        <v>108194</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80394</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219711</v>
+        <v>515</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blylav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Pectenia plumbea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+          <t>(Lightf.) P.M.Jørg. et al.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lövskogslund, Lådnaön, Gällnö skärgård, Upl</t>
+          <t>Lådnaön, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>711270.0789314739</v>
+        <v>711126</v>
       </c>
       <c r="R6" t="n">
-        <v>6592254.425700218</v>
+        <v>6592433</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1229,22 +1193,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2018-07-08</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2008-07-08</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2018-07-08</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2008-07-08</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>I ögonhöjd på gammal ask ca 380m väst Skomakarviken.NÖ delen av nyckelbiotopen 10J 8d 12 i Skogsstyrelsens register.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,31 +1214,31 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Lövskogslund</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Fingal Gyllang</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Fingal Gyllang</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>72467060</v>
+        <v>67171886</v>
       </c>
       <c r="B7" t="n">
-        <v>78529</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80394</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1306,14 +1265,10 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1321,10 +1276,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>711270.0789314739</v>
+        <v>711270</v>
       </c>
       <c r="R7" t="n">
-        <v>6592254.425700218</v>
+        <v>6592254</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1351,27 +1306,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2018-07-08</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-08-12</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2018-07-08</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-08-12</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På gammal ask.</t>
+          <t>Flera förekomster på gammal ask.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1382,6 +1327,26 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Lövskogslund.</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1398,57 +1363,55 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>72467067</v>
+        <v>110268678</v>
       </c>
       <c r="B8" t="n">
-        <v>99398</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80394</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221235</v>
+        <v>515</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blylav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Pectenia plumbea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Lightf.) P.M.Jørg. et al.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lövskogslund, Lådnaön, Gällnö skärgård, Upl</t>
+          <t>Lådnaön, lövskog NV Sviudden, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>711270.0789314739</v>
+        <v>711110</v>
       </c>
       <c r="R8" t="n">
-        <v>6592254.425700218</v>
+        <v>6592415</v>
       </c>
       <c r="S8" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1472,22 +1435,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2018-07-08</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-21</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2018-07-08</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-21</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På liggande, nyligen fallen askstam med bark, till synes välmående bålar fortfarande.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1496,80 +1454,91 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Lövskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Fingal Gyllang</t>
+          <t>Rikard Anderberg</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Fingal Gyllang</t>
+          <t>Rikard Anderberg, Fingal Gyllang</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>86340912</v>
+        <v>110268654</v>
       </c>
       <c r="B9" t="n">
-        <v>97512</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>81024</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>174</v>
+        <v>737</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Strävlosta</t>
+          <t>Mörk kraterlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Bromopsis benekenii</t>
+          <t>Gyalecta truncigena</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Lange) Holub</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
+          <t>(Ach.) Hepp</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Lådnaön, Upl</t>
+          <t>Lådnaön, lövskog NV Sviudden, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>711299.7420976626</v>
+        <v>711105</v>
       </c>
       <c r="R9" t="n">
-        <v>6592235.685353119</v>
+        <v>6592285</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1596,22 +1565,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2020-06-18</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-21</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2020-06-18</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-21</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Sp. muriforma, täml. korta och breda med många cellväggar.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1620,81 +1584,96 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Lövskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>Gammalt träd, i skugga</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior # Gammalt träd, i skugga</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Patrik Engström</t>
+          <t>Rikard Anderberg</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Patrik Engström</t>
+          <t>Rikard Anderberg, Fingal Gyllang</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>94440647</v>
+        <v>110268669</v>
       </c>
       <c r="B10" t="n">
-        <v>101680</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>81024</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222412</v>
+        <v>737</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Mörk kraterlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Gyalecta truncigena</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(Ach.) Hepp</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Skogen innanför Skötsundet, Upl</t>
+          <t>Lådnaön, lövskog NV Sviudden, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>711250.5545615957</v>
+        <v>711110</v>
       </c>
       <c r="R10" t="n">
-        <v>6592174.272154144</v>
+        <v>6592415</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1721,103 +1700,108 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2021-06-23</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-21</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2021-06-23</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-21</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ej mikroskoperad.</t>
         </is>
       </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Lövskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Patrik Engström</t>
+          <t>Rikard Anderberg</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Patrik Engström</t>
+          <t>Rikard Anderberg, Fingal Gyllang</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>110268662</v>
+        <v>67171938</v>
       </c>
       <c r="B11" t="n">
-        <v>79636</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>145</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Klosterlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Biatoridium monasteriense</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>J.Lahm ex Körb.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lådnaön, lövskog NV Sviudden, Upl</t>
+          <t>Lövskogslund, Lådnaön, Gällnö skärgård, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>711109.8607734053</v>
+        <v>711270</v>
       </c>
       <c r="R11" t="n">
-        <v>6592414.787571788</v>
+        <v>6592254</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1841,22 +1825,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-06-21</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-08-12</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-06-21</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-08-12</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1865,39 +1839,18 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>Lövskog</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>ask</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Rikard Anderberg</t>
+          <t>Fingal Gyllang</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Rikard Anderberg, Fingal Gyllang</t>
+          <t>Fingal Gyllang</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1907,12 +1860,7 @@
         <v>110268673</v>
       </c>
       <c r="B12" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1947,10 +1895,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>711109.8607734053</v>
+        <v>711110</v>
       </c>
       <c r="R12" t="n">
-        <v>6592414.787571788</v>
+        <v>6592415</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1980,19 +1928,9 @@
           <t>2023-06-21</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2023-06-21</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2040,37 +1978,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>110268669</v>
+        <v>110269387</v>
       </c>
       <c r="B13" t="n">
-        <v>79135</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>737</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kraterlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Gyalecta truncigena</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Hepp</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2079,17 +2012,17 @@
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lådnaön, lövskog NV Sviudden, Upl</t>
+          <t>Lövlund, LÅdnaön, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>711109.8607734053</v>
+        <v>711105</v>
       </c>
       <c r="R13" t="n">
-        <v>6592414.787571788</v>
+        <v>6592425</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2116,122 +2049,78 @@
           <t>2023-06-21</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2023-06-21</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ej mikroskoperad.</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF13" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>Lövskog</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>ask</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Rikard Anderberg</t>
+          <t>Fingal Gyllang</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Rikard Anderberg, Fingal Gyllang</t>
+          <t>Fingal Gyllang, Rikard Anderberg</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>110269389</v>
+        <v>72467065</v>
       </c>
       <c r="B14" t="n">
-        <v>79636</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>111390</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>145</v>
+        <v>219711</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Klosterlav</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Biatoridium monasteriense</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>J.Lahm ex Körb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lövlund, LÅdnaön, Upl</t>
+          <t>Lövskogslund, Lådnaön, Gällnö skärgård, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>711105.6977136013</v>
+        <v>711270</v>
       </c>
       <c r="R14" t="n">
-        <v>6592425.265182833</v>
+        <v>6592254</v>
       </c>
       <c r="S14" t="n">
         <v>50</v>
@@ -2258,22 +2147,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2023-06-21</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-07-08</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2023-06-21</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-07-08</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2293,65 +2172,56 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Fingal Gyllang, Rikard Anderberg</t>
+          <t>Fingal Gyllang</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>110269393</v>
+        <v>72467067</v>
       </c>
       <c r="B15" t="n">
-        <v>98431</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102241</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222771</v>
+        <v>221235</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Lövlund, LÅdnaön, Upl</t>
+          <t>Lövskogslund, Lådnaön, Gällnö skärgård, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>711105.6977136013</v>
+        <v>711270</v>
       </c>
       <c r="R15" t="n">
-        <v>6592425.265182833</v>
+        <v>6592254</v>
       </c>
       <c r="S15" t="n">
         <v>50</v>
@@ -2378,22 +2248,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2023-06-21</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-07-08</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2023-06-21</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-07-08</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2413,63 +2273,67 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Fingal Gyllang, Rikard Anderberg</t>
+          <t>Fingal Gyllang</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>110269387</v>
+        <v>94440647</v>
       </c>
       <c r="B16" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104628</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>222412</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Lövlund, LÅdnaön, Upl</t>
+          <t>Skogen innanför Skötsundet, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>711105.6977136013</v>
+        <v>711251</v>
       </c>
       <c r="R16" t="n">
-        <v>6592425.265182833</v>
+        <v>6592174</v>
       </c>
       <c r="S16" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2493,22 +2357,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2023-06-21</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-06-23</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2023-06-21</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-06-23</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2517,75 +2371,67 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Fingal Gyllang</t>
+          <t>Patrik Engström</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Fingal Gyllang, Rikard Anderberg</t>
+          <t>Patrik Engström</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>110268678</v>
+        <v>66786502</v>
       </c>
       <c r="B17" t="n">
-        <v>78529</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>101228</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>515</v>
+        <v>222771</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blylav</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pectenia plumbea</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Lightf.) P.M.Jørg. et al.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Lådnaön, lövskog NV Sviudden, Upl</t>
+          <t>Lådnaön, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>711109.8607734053</v>
+        <v>711397</v>
       </c>
       <c r="R17" t="n">
-        <v>6592414.787571788</v>
+        <v>6592122</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2612,27 +2458,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2023-06-21</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-07-20</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2023-06-21</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>På liggande, nyligen fallen askstam med bark, till synes välmående bålar fortfarande.</t>
+          <t>2017-07-20</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2641,99 +2472,74 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>Lövskog</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>ask</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Rikard Anderberg</t>
+          <t>Patrik Engström</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Rikard Anderberg, Fingal Gyllang</t>
+          <t>Patrik Engström</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>110268654</v>
+        <v>110269393</v>
       </c>
       <c r="B18" t="n">
-        <v>79143</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101228</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>737</v>
+        <v>222771</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mörk kraterlav</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Gyalecta truncigena</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Hepp</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lådnaön, lövskog NV Sviudden, Upl</t>
+          <t>Lövlund, LÅdnaön, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>711105.4047380188</v>
+        <v>711105</v>
       </c>
       <c r="R18" t="n">
-        <v>6592284.477379236</v>
+        <v>6592425</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2760,74 +2566,29 @@
           <t>2023-06-21</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2023-06-21</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Sp. muriforma, täml. korta och breda med många cellväggar.</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
-      </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>Lövskog</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>ask</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
-      </c>
-      <c r="AL18" t="inlineStr">
-        <is>
-          <t>Gammalt träd, i skugga</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior # Gammalt träd, i skugga</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Rikard Anderberg</t>
+          <t>Fingal Gyllang</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Rikard Anderberg, Fingal Gyllang</t>
+          <t>Fingal Gyllang, Rikard Anderberg</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>

--- a/artfynd/A 23767-2026 artfynd.xlsx
+++ b/artfynd/A 23767-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AZ18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -797,6 +802,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110268662</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -901,6 +911,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110269389</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1001,6 +1016,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66786499</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1111,6 +1131,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86340912</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1232,6 +1257,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/175596</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1360,6 +1390,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67171886</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1490,6 +1525,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110268678</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1629,6 +1669,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110268654</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1755,6 +1800,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110268669</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1854,6 +1904,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67171938</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1975,6 +2030,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110268673</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2075,6 +2135,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110269387</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2176,6 +2241,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72467065</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2277,6 +2347,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72467067</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2387,6 +2462,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94440647</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2487,6 +2567,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66786502</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2592,8 +2677,32 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110269393</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>